--- a/database/defaults/Standards_Calc_Database_Finalised.xlsx
+++ b/database/defaults/Standards_Calc_Database_Finalised.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\JFC\04_Software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53A83EC-F070-4258-9E69-E55BD2213754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{803E6AE5-E07B-4584-9E25-782BE1E59D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calc_rules" sheetId="1" r:id="rId1"/>
     <sheet name="ui_structure" sheetId="2" r:id="rId2"/>
     <sheet name="frl_reference" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="365">
   <si>
     <t>system</t>
   </si>
@@ -613,9 +616,15 @@
     <t>Info</t>
   </si>
   <si>
+    <t>Requires FRL</t>
+  </si>
+  <si>
     <t>Means of Detection</t>
   </si>
   <si>
+    <t>Smoke detection system</t>
+  </si>
+  <si>
     <t>Smoke Detectors</t>
   </si>
   <si>
@@ -628,36 +637,42 @@
     <t>Total Quantity,Grid Spacing,Coverage Area,Formula</t>
   </si>
   <si>
+    <t>units</t>
+  </si>
+  <si>
+    <t>Heat detection system</t>
+  </si>
+  <si>
     <t>Heat Detectors</t>
   </si>
   <si>
     <t>Heat Detector</t>
   </si>
   <si>
-    <t>Aspirating Units</t>
+    <t>Aspirating smoke detection system</t>
+  </si>
+  <si>
+    <t>Aspirating Detectors</t>
   </si>
   <si>
     <t>Aspirating Unit</t>
   </si>
   <si>
-    <t>Sampling</t>
+    <t>Aspirating Detector Pipework</t>
   </si>
   <si>
     <t>Sampling Pipework</t>
   </si>
   <si>
-    <t>units</t>
-  </si>
-  <si>
-    <t>Sampling Points</t>
-  </si>
-  <si>
-    <t>Sampling Point</t>
+    <t>kg</t>
   </si>
   <si>
     <t>Manual Call Points</t>
   </si>
   <si>
+    <t>Manual call point</t>
+  </si>
+  <si>
     <t>Fire Indicator Panels</t>
   </si>
   <si>
@@ -667,7 +682,25 @@
     <t>Means of Warning</t>
   </si>
   <si>
-    <t>Audio</t>
+    <t>Visual warning system</t>
+  </si>
+  <si>
+    <t>Visual Alarm Devices</t>
+  </si>
+  <si>
+    <t>Visual alarm device</t>
+  </si>
+  <si>
+    <t>Total Quantity,Grid Spacing,Coverage Area</t>
+  </si>
+  <si>
+    <t>EWIS / voice alarm system</t>
+  </si>
+  <si>
+    <t>EWIS Panels</t>
+  </si>
+  <si>
+    <t>EWIS panel</t>
   </si>
   <si>
     <t>Speakers</t>
@@ -676,241 +709,292 @@
     <t>Speaker</t>
   </si>
   <si>
-    <t>Total Quantity,Grid Spacing,Coverage Area</t>
-  </si>
-  <si>
-    <t>Speaker Batteries</t>
-  </si>
-  <si>
-    <t>Battery</t>
+    <t>Amplifiers</t>
+  </si>
+  <si>
+    <t>Amplifier</t>
+  </si>
+  <si>
+    <t>Audible Warning System</t>
+  </si>
+  <si>
+    <t>Sounders</t>
+  </si>
+  <si>
+    <t>Sounder</t>
+  </si>
+  <si>
+    <t>Cabling</t>
+  </si>
+  <si>
+    <t>Fire-Rated Cabling</t>
+  </si>
+  <si>
+    <t>Non-Fire-Rated Cabling</t>
+  </si>
+  <si>
+    <t>Means of Egress</t>
+  </si>
+  <si>
+    <t>Emergency lighting system</t>
+  </si>
+  <si>
+    <t>Emergency Luminaires</t>
+  </si>
+  <si>
+    <t>Emergency Luminaire</t>
+  </si>
+  <si>
+    <t>Exit signage system</t>
+  </si>
+  <si>
+    <t>Illuminated Exit Signs</t>
+  </si>
+  <si>
+    <t>Illuminated Exit Sign</t>
+  </si>
+  <si>
+    <t>Total Quantity</t>
+  </si>
+  <si>
+    <t>Means of First Aid Fire-Fighting</t>
+  </si>
+  <si>
+    <t>Portable Extinguisher System</t>
+  </si>
+  <si>
+    <t>Extinguishers</t>
+  </si>
+  <si>
+    <t>Fire extinguishers</t>
+  </si>
+  <si>
+    <t>Hose Reels</t>
+  </si>
+  <si>
+    <t>Hose Reel Assembly</t>
+  </si>
+  <si>
+    <t>Hose reel , Cabinet, Fire Hose Reel, Hose reel valve</t>
+  </si>
+  <si>
+    <t>reels</t>
+  </si>
+  <si>
+    <t>Hose Reel Pipework</t>
+  </si>
+  <si>
+    <t>Pipework</t>
+  </si>
+  <si>
+    <t>Means of Restricting Fire Spread / Structural Protection</t>
+  </si>
+  <si>
+    <t>Fire-rated Wall Assembly</t>
+  </si>
+  <si>
+    <t>Plasterboard Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Resistant Plasterboard </t>
+  </si>
+  <si>
+    <t>Required FRL is a direct user override (no NCC lookup is performed) - select the Product Type matching the required FRL and construction thickness. Carbon factors assume a standard reference density to convert the manufacturer's per-kg factor to a per-m² wall rate, since no project-specific density was supplied.</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Speed Panel Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed Panel </t>
+  </si>
+  <si>
+    <t>Masonry Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masonry </t>
+  </si>
+  <si>
+    <t>Concrete Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete </t>
+  </si>
+  <si>
+    <t>Doors and Glazing</t>
+  </si>
+  <si>
+    <t>Fire Doors</t>
+  </si>
+  <si>
+    <t>Fire Door</t>
+  </si>
+  <si>
+    <t>Fire Doors (Steel with Glazing)</t>
+  </si>
+  <si>
+    <t>Fire Door(Steel with Glazing)</t>
+  </si>
+  <si>
+    <t>Fire Resistant Glazing</t>
+  </si>
+  <si>
+    <t>Glass Glazing</t>
+  </si>
+  <si>
+    <t>Shutters, Curtains and Dampers</t>
+  </si>
+  <si>
+    <t>Fire Shutters</t>
+  </si>
+  <si>
+    <t>Fire Shutter</t>
+  </si>
+  <si>
+    <t>Fire Curtains</t>
+  </si>
+  <si>
+    <t>Fire Curtain</t>
+  </si>
+  <si>
+    <t>Fusible link damper</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual duct size being protected.</t>
+  </si>
+  <si>
+    <t>Penetration and Joint Fire-Stopping</t>
+  </si>
+  <si>
+    <t>Fire Batts</t>
+  </si>
+  <si>
+    <t>Mastic Fire batt</t>
+  </si>
+  <si>
+    <t>Intumescent Collars</t>
+  </si>
+  <si>
+    <t>Fire collar</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual pipe diameter being protected.</t>
+  </si>
+  <si>
+    <t>Fire-Resistant Joint Seals</t>
+  </si>
+  <si>
+    <t>Fire-Resistant Joint Seal</t>
+  </si>
+  <si>
+    <t>seals</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual joint/pipe size being protected.</t>
+  </si>
+  <si>
+    <t>Intumescent Pipe Wraps</t>
+  </si>
+  <si>
+    <t>Intumescent Pipe Wrap</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual pipe diameter being wrapped.</t>
+  </si>
+  <si>
+    <t>Fire-Resistant Mastic</t>
+  </si>
+  <si>
+    <t>kg,L</t>
+  </si>
+  <si>
+    <t>Structural Fire Protection</t>
+  </si>
+  <si>
+    <t>Intumescent coating</t>
+  </si>
+  <si>
+    <t>Spray-Applied Fire Protection</t>
+  </si>
+  <si>
+    <t>Spray</t>
+  </si>
+  <si>
+    <t>Means of Suppression</t>
+  </si>
+  <si>
+    <t>Sprinklers</t>
+  </si>
+  <si>
+    <t>Sprinkler Heads</t>
+  </si>
+  <si>
+    <t>Sprinkler Head</t>
+  </si>
+  <si>
+    <t>Sprinkler Pipework</t>
+  </si>
+  <si>
+    <t>Total Quantity,Formula</t>
+  </si>
+  <si>
+    <t>vertical_riser_formula,horizontal_pipe_formula</t>
+  </si>
+  <si>
+    <t>The Formula option is an early-stage geometric approximation, not a cited AS clause - verify before relying on it for design.</t>
+  </si>
+  <si>
+    <t>Sprinkler Valves</t>
+  </si>
+  <si>
+    <t>Sprinkler Valve</t>
   </si>
   <si>
     <t>Linked Child</t>
   </si>
   <si>
-    <t>Override Only</t>
-  </si>
-  <si>
-    <t>Amplifiers</t>
-  </si>
-  <si>
-    <t>Amplifier</t>
-  </si>
-  <si>
-    <t>Amplifier Batteries</t>
-  </si>
-  <si>
-    <t>Sounders</t>
-  </si>
-  <si>
-    <t>Sounder</t>
-  </si>
-  <si>
-    <t>Sounder Batteries</t>
-  </si>
-  <si>
-    <t>Sounder Bases</t>
-  </si>
-  <si>
-    <t>Sounder Base</t>
-  </si>
-  <si>
     <t>Choice</t>
   </si>
   <si>
-    <t>Cabling</t>
-  </si>
-  <si>
-    <t>Fire-Rated Cabling</t>
-  </si>
-  <si>
-    <t>Non-Fire-Rated Cabling</t>
-  </si>
-  <si>
-    <t>EWIS Panels</t>
-  </si>
-  <si>
-    <t>EWIS Panel Batteries</t>
-  </si>
-  <si>
-    <t>Visual Alarm Devices</t>
-  </si>
-  <si>
-    <t>Visual Alarm Device Batteries</t>
-  </si>
-  <si>
-    <t>Mounting Bases</t>
-  </si>
-  <si>
-    <t>Mounting Base</t>
-  </si>
-  <si>
-    <t>Means of First Aid Fire-Fighting</t>
-  </si>
-  <si>
-    <t>Hose Reels</t>
-  </si>
-  <si>
-    <t>Hose Reel Assembly</t>
-  </si>
-  <si>
-    <t>reels</t>
-  </si>
-  <si>
-    <t>Hose Reel Pipework</t>
-  </si>
-  <si>
-    <t>Pipework</t>
-  </si>
-  <si>
-    <t>Means of Restricting Fire Spread / Structural Protection</t>
-  </si>
-  <si>
-    <t>Wall Assemblies</t>
-  </si>
-  <si>
-    <t>Plasterboard Wall Assembly</t>
-  </si>
-  <si>
-    <t>Required FRL is a direct user override (no NCC lookup is performed) - select the Product Type matching the required FRL and construction thickness. Carbon factors assume a standard reference density to convert the manufacturer's per-kg factor to a per-m² wall rate, since no project-specific density was supplied.</t>
-  </si>
-  <si>
-    <t>Speed Panel Wall Assembly</t>
-  </si>
-  <si>
-    <t>Masonry Wall Assembly</t>
-  </si>
-  <si>
-    <t>Concrete Wall Assembly</t>
-  </si>
-  <si>
-    <t>Fire Batts</t>
-  </si>
-  <si>
-    <t>Mastic Fire batt</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Fire Doors</t>
-  </si>
-  <si>
-    <t>Fire Door</t>
+    <t>Water Supply Equipments</t>
+  </si>
+  <si>
+    <t>Pump sets</t>
+  </si>
+  <si>
+    <t>Means of Smoke Hazard Management</t>
+  </si>
+  <si>
+    <t>Smoke Exhaust Fan</t>
+  </si>
+  <si>
+    <t>Smoke Exhaust Fan (notional - 1000mm)</t>
+  </si>
+  <si>
+    <t>Smoke Subducts</t>
+  </si>
+  <si>
+    <t>Ensure the selected product matches the desired duct size.</t>
+  </si>
+  <si>
+    <t>Motorized Smoke Dampers</t>
+  </si>
+  <si>
+    <t>Motorized Dampers</t>
+  </si>
+  <si>
+    <t>Smoke Doors</t>
+  </si>
+  <si>
+    <t>Smoke Door</t>
   </si>
   <si>
     <t>doors</t>
   </si>
   <si>
-    <t>Smoke Doors</t>
-  </si>
-  <si>
-    <t>Smoke Door</t>
-  </si>
-  <si>
-    <t>Non-Fire-Rated Doors</t>
-  </si>
-  <si>
-    <t>Non-Fire-Rated Door</t>
-  </si>
-  <si>
-    <t>Fire Resistant Glazing</t>
-  </si>
-  <si>
-    <t>Glass Glazing</t>
-  </si>
-  <si>
-    <t>Heat Strengthened Glazing</t>
-  </si>
-  <si>
-    <t>Pipework Protection</t>
-  </si>
-  <si>
-    <t>Intumescent Collars</t>
-  </si>
-  <si>
-    <t>Fire collar</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual pipe diameter being protected.</t>
-  </si>
-  <si>
-    <t>Fire-Resistant Joint Seals</t>
-  </si>
-  <si>
-    <t>Fire-Resistant Joint Seal</t>
-  </si>
-  <si>
-    <t>seals</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual joint/pipe size being protected.</t>
-  </si>
-  <si>
-    <t>Intumescent Pipe Wraps</t>
-  </si>
-  <si>
-    <t>Intumescent Pipe Wrap</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual pipe diameter being wrapped.</t>
-  </si>
-  <si>
-    <t>Fire-Resistant Mastic</t>
-  </si>
-  <si>
-    <t>kg,L</t>
-  </si>
-  <si>
-    <t>Fire-Stop Mortar</t>
-  </si>
-  <si>
-    <t>Applied Structural Fire Protection</t>
-  </si>
-  <si>
-    <t>Fire Shutters</t>
-  </si>
-  <si>
-    <t>Fire Shutter</t>
-  </si>
-  <si>
-    <t>Fire Curtains</t>
-  </si>
-  <si>
-    <t>Fire Curtain</t>
-  </si>
-  <si>
-    <t>Means of Suppression</t>
-  </si>
-  <si>
-    <t>Sprinklers</t>
-  </si>
-  <si>
-    <t>Sprinkler Heads</t>
-  </si>
-  <si>
-    <t>Sprinkler Head</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Sprinkler Pipework</t>
-  </si>
-  <si>
-    <t>Total Quantity,Formula</t>
-  </si>
-  <si>
-    <t>vertical_riser_formula,horizontal_pipe_formula</t>
-  </si>
-  <si>
-    <t>The Formula option is an early-stage geometric approximation, not a cited AS clause - verify before relying on it for design.</t>
-  </si>
-  <si>
-    <t>Sprinkler Valves</t>
-  </si>
-  <si>
-    <t>Sprinkler Valve</t>
+    <t>Means of Fire Brigade Access and Intervention</t>
   </si>
   <si>
     <t>Hydrants</t>
@@ -937,34 +1021,10 @@
     <t>Typically 1 booster assembly per hydrant system - confirm against site layout and AS2419.1.</t>
   </si>
   <si>
-    <t>Means of Smoke Hazard Management</t>
-  </si>
-  <si>
-    <t>Smoke Exhaust Fans</t>
-  </si>
-  <si>
-    <t>Fire Resistant Ductwork</t>
-  </si>
-  <si>
-    <t>Ensure the selected product matches the desired duct size.</t>
-  </si>
-  <si>
-    <t>Regular Sheet Metal Ductwork</t>
-  </si>
-  <si>
-    <t>Means of Fire Brigade Access and Intervention</t>
-  </si>
-  <si>
-    <t>Fire Control Centre</t>
-  </si>
-  <si>
-    <t>centres</t>
-  </si>
-  <si>
     <t>Fire Safety Management</t>
   </si>
   <si>
-    <t>signs</t>
+    <t>Fire safety signage system</t>
   </si>
   <si>
     <t>Evacuation Diagram Systems</t>
@@ -988,30 +1048,6 @@
     <t>Portable Extinguishers,Hose Reel Assembly,Hydrant Valves,Hydrant Boosters</t>
   </si>
   <si>
-    <t>Means of Egress</t>
-  </si>
-  <si>
-    <t>Emergency Luminaires</t>
-  </si>
-  <si>
-    <t>Emergency Luminaire</t>
-  </si>
-  <si>
-    <t>Illuminated Exit Signs</t>
-  </si>
-  <si>
-    <t>Illuminated Exit Sign</t>
-  </si>
-  <si>
-    <t>Total Quantity</t>
-  </si>
-  <si>
-    <t>Directional Exit Signs</t>
-  </si>
-  <si>
-    <t>Directional Exit Sign</t>
-  </si>
-  <si>
     <t>Special Hazards</t>
   </si>
   <si>
@@ -1033,118 +1069,37 @@
     <t>Atrium Fire and Smoke-Control Systems</t>
   </si>
   <si>
-    <t>Motorized Dampers</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual duct size being protected.</t>
-  </si>
-  <si>
-    <t>Fusible link damper</t>
-  </si>
-  <si>
-    <t>Fire Doors (Steel with Glazing)</t>
-  </si>
-  <si>
-    <t>Fire Door(Steel with Glazing)</t>
-  </si>
-  <si>
-    <t>Hose reel , Cabinet, Fire Hose Reel, Hose reel valve</t>
-  </si>
-  <si>
-    <t>Portable Extinguisher</t>
-  </si>
-  <si>
-    <t>Extinguishers</t>
-  </si>
-  <si>
-    <t>Fire extinguishers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Resistant Plasterboard </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed Panel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masonry </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete </t>
-  </si>
-  <si>
-    <t>Penetration Fire-Stopping</t>
-  </si>
-  <si>
-    <t>Doors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doors </t>
-  </si>
-  <si>
-    <t>Fire-Resistant Glazing</t>
-  </si>
-  <si>
-    <t>Water Supply Equipments</t>
-  </si>
-  <si>
-    <t>Smoke Exhaust Fan (notional - 1000mm)</t>
-  </si>
-  <si>
-    <t>Fire/Smoke Damper</t>
-  </si>
-  <si>
-    <t>Smoke Subducts 1</t>
-  </si>
-  <si>
-    <t>Smoke Subducts 2</t>
-  </si>
-  <si>
-    <t>EWIS panel</t>
-  </si>
-  <si>
-    <t>Visual alarm device</t>
-  </si>
-  <si>
-    <t>Manual call point</t>
-  </si>
-  <si>
-    <t>End-Suction Centrifugal Pumpset</t>
-  </si>
-  <si>
-    <t>Vertical Multistage Jacking Pumpset</t>
-  </si>
-  <si>
-    <t>Pumpset 1</t>
-  </si>
-  <si>
-    <t>Pumpset 2</t>
-  </si>
-  <si>
-    <t>Small Signs</t>
-  </si>
-  <si>
-    <t>Medium Signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input </t>
-  </si>
-  <si>
-    <t>Fire Safety Signage 1</t>
-  </si>
-  <si>
-    <t>Fire Safety Signage 2</t>
-  </si>
-  <si>
-    <t>Fire Damper 1</t>
-  </si>
-  <si>
-    <t>Fire Damper 2</t>
-  </si>
-  <si>
-    <t>Intumescent Coating</t>
-  </si>
-  <si>
-    <t>Intumescent coating</t>
+    <t>Things to do</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>1. Check which one exclude</t>
+  </si>
+  <si>
+    <t>Things to work on</t>
+  </si>
+  <si>
+    <t>2. Check which one for future implementation (Think how we show this)</t>
+  </si>
+  <si>
+    <t>Exclude</t>
+  </si>
+  <si>
+    <t>3. Check which one we need to put but not on the list (Future implementation)</t>
+  </si>
+  <si>
+    <t>Future Implementation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Are they in right group? Naming correct? </t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed </t>
   </si>
   <si>
     <t>Product Type</t>
@@ -1178,16 +1133,13 @@
   </si>
   <si>
     <t>13mm</t>
-  </si>
-  <si>
-    <t>Requires FRL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1201,8 +1153,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1217,42 +1180,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor rgb="FFFF66FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF7C80"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF66FF"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1260,22 +1241,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1584,9 +1624,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H97"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1612,7 +1652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1638,7 +1678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1664,7 +1704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1690,7 +1730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1716,7 +1756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1742,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1768,7 +1808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1794,7 +1834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1820,7 +1860,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1846,7 +1886,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1872,7 +1912,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1898,7 +1938,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -1924,7 +1964,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1950,7 +1990,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1976,7 +2016,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2002,7 +2042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -2028,7 +2068,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -2054,7 +2094,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -2080,7 +2120,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>59</v>
       </c>
@@ -2106,7 +2146,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -2132,7 +2172,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -2158,7 +2198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -2184,7 +2224,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -2210,7 +2250,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -2236,7 +2276,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -2262,7 +2302,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -2288,7 +2328,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -2314,7 +2354,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -2340,7 +2380,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -2366,7 +2406,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2392,7 +2432,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -2418,7 +2458,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>59</v>
       </c>
@@ -2444,7 +2484,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -2470,7 +2510,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>59</v>
       </c>
@@ -2496,7 +2536,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -2522,7 +2562,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -2548,7 +2588,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>59</v>
       </c>
@@ -2574,7 +2614,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -2600,7 +2640,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>59</v>
       </c>
@@ -2626,7 +2666,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>59</v>
       </c>
@@ -2652,7 +2692,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -2678,7 +2718,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -2704,7 +2744,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -2730,7 +2770,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -2756,7 +2796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2782,7 +2822,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -2808,7 +2848,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2834,7 +2874,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -2860,7 +2900,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -2886,7 +2926,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -2912,7 +2952,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2938,7 +2978,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -2964,7 +3004,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -2990,7 +3030,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -3016,7 +3056,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -3042,7 +3082,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -3068,7 +3108,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -3094,7 +3134,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -3120,7 +3160,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -3146,7 +3186,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -3172,7 +3212,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -3198,7 +3238,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>59</v>
       </c>
@@ -3224,7 +3264,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>59</v>
       </c>
@@ -3250,7 +3290,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>59</v>
       </c>
@@ -3276,7 +3316,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -3302,7 +3342,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
         <v>59</v>
       </c>
@@ -3328,7 +3368,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
         <v>59</v>
       </c>
@@ -3354,7 +3394,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
         <v>59</v>
       </c>
@@ -3380,7 +3420,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
         <v>59</v>
       </c>
@@ -3406,7 +3446,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
         <v>59</v>
       </c>
@@ -3432,7 +3472,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
         <v>59</v>
       </c>
@@ -3458,7 +3498,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>59</v>
       </c>
@@ -3484,7 +3524,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
         <v>59</v>
       </c>
@@ -3510,7 +3550,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -3536,7 +3576,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
         <v>59</v>
       </c>
@@ -3562,7 +3602,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -3588,7 +3628,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -3614,7 +3654,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
         <v>118</v>
       </c>
@@ -3640,7 +3680,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -3666,7 +3706,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>131</v>
       </c>
@@ -3692,7 +3732,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>131</v>
       </c>
@@ -3718,7 +3758,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>131</v>
       </c>
@@ -3744,7 +3784,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>131</v>
       </c>
@@ -3770,7 +3810,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>131</v>
       </c>
@@ -3796,7 +3836,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>147</v>
       </c>
@@ -3822,7 +3862,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>147</v>
       </c>
@@ -3848,7 +3888,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>147</v>
       </c>
@@ -3874,7 +3914,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>147</v>
       </c>
@@ -3900,7 +3940,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>160</v>
       </c>
@@ -3926,7 +3966,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>160</v>
       </c>
@@ -3952,7 +3992,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>160</v>
       </c>
@@ -3978,7 +4018,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>160</v>
       </c>
@@ -4004,7 +4044,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
         <v>160</v>
       </c>
@@ -4030,7 +4070,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>42</v>
       </c>
@@ -4056,7 +4096,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>42</v>
       </c>
@@ -4082,7 +4122,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>42</v>
       </c>
@@ -4115,26 +4155,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R71"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R81"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="17" width="20" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>175</v>
       </c>
       <c r="B1" t="s">
         <v>176</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F1" t="s">
@@ -4174,27 +4218,33 @@
         <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G2" t="s">
-        <v>196</v>
+        <v>198</v>
+      </c>
+      <c r="I2" t="s">
+        <v>199</v>
       </c>
       <c r="L2" t="s">
         <v>42</v>
@@ -4206,21 +4256,30 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3" spans="1:18" ht="15">
+      <c r="A3" s="22">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>200</v>
+      </c>
       <c r="D3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" t="s">
         <v>197</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>198</v>
       </c>
-      <c r="F3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" t="s">
-        <v>196</v>
+      <c r="I3" t="s">
+        <v>199</v>
       </c>
       <c r="L3" t="s">
         <v>42</v>
@@ -4232,21 +4291,30 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:18" ht="15">
+      <c r="A4" s="22">
         <v>1</v>
       </c>
+      <c r="B4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>203</v>
+      </c>
       <c r="D4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G4" t="s">
+        <v>198</v>
+      </c>
+      <c r="I4" t="s">
         <v>199</v>
-      </c>
-      <c r="E4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" t="s">
-        <v>196</v>
       </c>
       <c r="L4" t="s">
         <v>42</v>
@@ -4258,1384 +4326,1247 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A5" s="22">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="B5" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15">
+      <c r="A6" s="22">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15">
+      <c r="A7" s="22">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15">
+      <c r="A8" s="23">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15">
+      <c r="A9" s="23">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A10" s="23">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A11" s="23">
+        <v>2</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A12" s="23">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A13" s="23">
+        <v>2</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A14" s="23">
+        <v>2</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15">
+      <c r="A15" s="22">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" t="s">
+        <v>217</v>
+      </c>
+      <c r="I15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15">
+      <c r="A16" s="22">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" t="s">
+        <v>237</v>
+      </c>
+      <c r="F16" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" t="s">
+        <v>238</v>
+      </c>
+      <c r="I16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="21" customFormat="1" ht="15">
+      <c r="A17" s="23">
+        <v>4</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15">
+      <c r="A18" s="23">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D18" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="F18" t="s">
+        <v>197</v>
+      </c>
+      <c r="I18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A19" s="23">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15">
+      <c r="A20" s="22">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E7" t="s">
-        <v>356</v>
-      </c>
-      <c r="F7" t="s">
-        <v>195</v>
-      </c>
-      <c r="I7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>207</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="E20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F20" t="s">
+        <v>197</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P20" t="s">
+        <v>253</v>
+      </c>
+      <c r="R20" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15">
+      <c r="A21" s="22">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" t="s">
+        <v>255</v>
+      </c>
+      <c r="E21" t="s">
+        <v>256</v>
+      </c>
+      <c r="F21" t="s">
+        <v>197</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P21" t="s">
+        <v>253</v>
+      </c>
+      <c r="R21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15">
+      <c r="A22" s="22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" t="s">
+        <v>258</v>
+      </c>
+      <c r="F22" t="s">
+        <v>197</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P22" t="s">
+        <v>253</v>
+      </c>
+      <c r="R22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15">
+      <c r="A23" s="22">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" t="s">
+        <v>260</v>
+      </c>
+      <c r="F23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15">
+      <c r="A24" s="22">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E24" t="s">
+        <v>263</v>
+      </c>
+      <c r="F24" t="s">
+        <v>197</v>
+      </c>
+      <c r="I24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15">
+      <c r="A25" s="22">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" t="s">
+        <v>197</v>
+      </c>
+      <c r="I25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15">
+      <c r="A26" s="22">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D26" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F26" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15">
+      <c r="A27" s="22">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D27" t="s">
+        <v>269</v>
+      </c>
+      <c r="E27" t="s">
+        <v>270</v>
+      </c>
+      <c r="F27" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15">
+      <c r="A28" s="22">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28" t="s">
+        <v>271</v>
+      </c>
+      <c r="E28" t="s">
+        <v>272</v>
+      </c>
+      <c r="F28" t="s">
+        <v>197</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15">
+      <c r="A29" s="22">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" t="s">
+        <v>273</v>
+      </c>
+      <c r="E29" t="s">
+        <v>273</v>
+      </c>
+      <c r="F29" t="s">
+        <v>197</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F9" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F10" t="s">
-        <v>216</v>
-      </c>
-      <c r="J10" t="s">
-        <v>211</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="P29" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15">
+      <c r="A30" s="22">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>249</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E30" t="s">
+        <v>277</v>
+      </c>
+      <c r="F30" t="s">
+        <v>197</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15">
+      <c r="A31" s="22">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D31" t="s">
+        <v>278</v>
+      </c>
+      <c r="E31" t="s">
+        <v>279</v>
+      </c>
+      <c r="F31" t="s">
+        <v>197</v>
+      </c>
+      <c r="I31" t="s">
+        <v>199</v>
+      </c>
+      <c r="P31" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A32" s="22">
+        <v>5</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A33" s="22">
+        <v>5</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A34" s="22">
+        <v>5</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15">
+      <c r="A35" s="22">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>249</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D35" t="s">
+        <v>291</v>
+      </c>
+      <c r="E35" t="s">
+        <v>291</v>
+      </c>
+      <c r="F35" t="s">
+        <v>197</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A36" s="22">
+        <v>5</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15">
+      <c r="A37" s="23">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>294</v>
+      </c>
+      <c r="C37" t="s">
+        <v>295</v>
+      </c>
+      <c r="D37" t="s">
+        <v>296</v>
+      </c>
+      <c r="E37" t="s">
+        <v>297</v>
+      </c>
+      <c r="F37" t="s">
+        <v>197</v>
+      </c>
+      <c r="G37" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F11" t="s">
-        <v>195</v>
-      </c>
-      <c r="I11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" t="s">
-        <v>216</v>
-      </c>
-      <c r="J12" t="s">
-        <v>218</v>
-      </c>
-      <c r="K12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>210</v>
-      </c>
-      <c r="D13" t="s">
-        <v>221</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F13" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>210</v>
-      </c>
-      <c r="D14" t="s">
-        <v>223</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F14" t="s">
-        <v>216</v>
-      </c>
-      <c r="J14" t="s">
-        <v>221</v>
-      </c>
-      <c r="K14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F15" t="s">
-        <v>216</v>
-      </c>
-      <c r="J15" t="s">
-        <v>221</v>
-      </c>
-      <c r="K15" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" t="s">
-        <v>228</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F16" t="s">
-        <v>195</v>
-      </c>
-      <c r="I16" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>227</v>
-      </c>
-      <c r="D17" t="s">
-        <v>229</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F17" t="s">
-        <v>195</v>
-      </c>
-      <c r="I17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>230</v>
-      </c>
-      <c r="D18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F18" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>230</v>
-      </c>
-      <c r="D19" t="s">
-        <v>231</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F19" t="s">
-        <v>216</v>
-      </c>
-      <c r="J19" t="s">
-        <v>230</v>
-      </c>
-      <c r="K19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D20" t="s">
-        <v>232</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F20" t="s">
-        <v>195</v>
-      </c>
-      <c r="G20" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>232</v>
-      </c>
-      <c r="D21" t="s">
-        <v>233</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F21" t="s">
-        <v>216</v>
-      </c>
-      <c r="J21" t="s">
-        <v>232</v>
-      </c>
-      <c r="K21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>232</v>
-      </c>
-      <c r="D22" t="s">
-        <v>234</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F22" t="s">
-        <v>216</v>
-      </c>
-      <c r="J22" t="s">
-        <v>232</v>
-      </c>
-      <c r="K22" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>236</v>
-      </c>
-      <c r="C23" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="H37" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15">
+      <c r="A38" s="23">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>294</v>
+      </c>
+      <c r="C38" t="s">
+        <v>295</v>
+      </c>
+      <c r="D38" t="s">
+        <v>298</v>
+      </c>
+      <c r="E38" t="s">
+        <v>298</v>
+      </c>
+      <c r="F38" t="s">
+        <v>197</v>
+      </c>
+      <c r="G38" t="s">
+        <v>299</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J38" t="s">
+        <v>296</v>
+      </c>
+      <c r="L38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
+        <v>300</v>
+      </c>
+      <c r="P38" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A39" s="23">
+        <v>6</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15">
+      <c r="A40" s="23">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>294</v>
+      </c>
+      <c r="C40" t="s">
+        <v>306</v>
+      </c>
+      <c r="D40" t="s">
+        <v>307</v>
+      </c>
+      <c r="E40" t="s">
+        <v>307</v>
+      </c>
+      <c r="F40" t="s">
+        <v>197</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15">
+      <c r="A41" s="22">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>308</v>
+      </c>
+      <c r="D41" t="s">
+        <v>309</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F41" t="s">
+        <v>197</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15">
+      <c r="A42" s="22">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>308</v>
+      </c>
+      <c r="D42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E42" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" t="s">
+        <v>197</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P42" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A43" s="22">
+        <v>7</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="P43" s="16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A44" s="22">
+        <v>7</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A45" s="23">
+        <v>8</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="P45" s="16" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A46" s="23">
+        <v>8</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A47" s="23">
+        <v>8</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="P47" s="16" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A48" s="22">
+        <v>9</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A49" s="22">
+        <v>9</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A50" s="22">
+        <v>9</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A51" s="23">
+        <v>10</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="F23" t="s">
-        <v>195</v>
-      </c>
-      <c r="I23" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>237</v>
-      </c>
-      <c r="D24" t="s">
-        <v>240</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F24" t="s">
-        <v>195</v>
-      </c>
-      <c r="I24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>4</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="F51" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D25" s="3" t="s">
+    </row>
+    <row r="52" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A52" s="23">
+        <v>10</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F52" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A53" s="23">
+        <v>10</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>242</v>
-      </c>
-      <c r="C26" t="s">
-        <v>243</v>
-      </c>
-      <c r="D26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="F53" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A54" s="23">
+        <v>10</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F26" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P26" t="s">
-        <v>245</v>
-      </c>
-      <c r="R26" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>5</v>
-      </c>
-      <c r="C27" t="s">
-        <v>243</v>
-      </c>
-      <c r="D27" t="s">
-        <v>246</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="F54" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A55" s="23">
+        <v>10</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="P27" t="s">
-        <v>245</v>
-      </c>
-      <c r="R27" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
-        <v>243</v>
-      </c>
-      <c r="D28" t="s">
-        <v>247</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="F55" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="B58" t="s">
         <v>343</v>
       </c>
-      <c r="F28" t="s">
-        <v>195</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="P28" t="s">
-        <v>245</v>
-      </c>
-      <c r="R28" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>5</v>
-      </c>
-      <c r="C29" t="s">
-        <v>243</v>
-      </c>
-      <c r="D29" t="s">
-        <v>248</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="F58" t="s">
         <v>344</v>
       </c>
-      <c r="F29" t="s">
-        <v>195</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="P29" t="s">
-        <v>245</v>
-      </c>
-      <c r="R29" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="59" spans="1:15">
+      <c r="B59" t="s">
         <v>345</v>
       </c>
-      <c r="D30" t="s">
-        <v>249</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F30" t="s">
-        <v>195</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>5</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="F59" s="1"/>
+      <c r="G59" t="s">
         <v>346</v>
       </c>
-      <c r="D31" t="s">
-        <v>252</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F31" t="s">
-        <v>195</v>
-      </c>
-      <c r="I31" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>5</v>
-      </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="60" spans="1:15">
+      <c r="B60" t="s">
         <v>347</v>
       </c>
-      <c r="D32" t="s">
-        <v>255</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F32" t="s">
-        <v>195</v>
-      </c>
-      <c r="I32" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>347</v>
-      </c>
-      <c r="D33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F33" t="s">
-        <v>195</v>
-      </c>
-      <c r="I33" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>5</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="F60" s="4"/>
+      <c r="G60" t="s">
         <v>348</v>
       </c>
-      <c r="D34" t="s">
-        <v>259</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I34" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>5</v>
-      </c>
-      <c r="C35" t="s">
-        <v>348</v>
-      </c>
-      <c r="D35" t="s">
-        <v>261</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F35" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
-        <v>262</v>
-      </c>
-      <c r="D36" t="s">
-        <v>263</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="F36" t="s">
-        <v>195</v>
-      </c>
-      <c r="I36" t="s">
-        <v>203</v>
-      </c>
-      <c r="P36" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>262</v>
-      </c>
-      <c r="D37" t="s">
-        <v>266</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37" t="s">
-        <v>268</v>
-      </c>
-      <c r="P37" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>262</v>
-      </c>
-      <c r="D38" t="s">
-        <v>270</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F38" t="s">
-        <v>195</v>
-      </c>
-      <c r="I38" t="s">
-        <v>109</v>
-      </c>
-      <c r="P38" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>5</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D39" t="s">
-        <v>369</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="F39" t="s">
-        <v>195</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>5</v>
-      </c>
-      <c r="D40" t="s">
-        <v>273</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F40" t="s">
-        <v>195</v>
-      </c>
-      <c r="I40" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>5</v>
-      </c>
-      <c r="D41" t="s">
-        <v>275</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F41" t="s">
-        <v>195</v>
-      </c>
-      <c r="I41" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>5</v>
-      </c>
-      <c r="D42" t="s">
-        <v>276</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F42" t="s">
-        <v>195</v>
-      </c>
-      <c r="I42" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>278</v>
-      </c>
-      <c r="D43" t="s">
-        <v>277</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="F43" t="s">
-        <v>195</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>5</v>
-      </c>
-      <c r="C44" t="s">
-        <v>280</v>
-      </c>
-      <c r="D44" t="s">
-        <v>279</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F44" t="s">
-        <v>195</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>281</v>
-      </c>
-      <c r="C45" t="s">
-        <v>282</v>
-      </c>
-      <c r="D45" t="s">
-        <v>283</v>
-      </c>
-      <c r="E45" t="s">
-        <v>284</v>
-      </c>
-      <c r="F45" t="s">
-        <v>195</v>
-      </c>
-      <c r="G45" t="s">
-        <v>213</v>
-      </c>
-      <c r="H45" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>6</v>
-      </c>
-      <c r="C46" t="s">
-        <v>282</v>
-      </c>
-      <c r="D46" t="s">
-        <v>286</v>
-      </c>
-      <c r="E46" t="s">
-        <v>286</v>
-      </c>
-      <c r="F46" t="s">
-        <v>195</v>
-      </c>
-      <c r="G46" t="s">
-        <v>287</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46" t="s">
-        <v>283</v>
-      </c>
-      <c r="L46" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" t="s">
-        <v>288</v>
-      </c>
-      <c r="P46" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>6</v>
-      </c>
-      <c r="C47" t="s">
-        <v>282</v>
-      </c>
-      <c r="D47" t="s">
-        <v>290</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F47" t="s">
-        <v>216</v>
-      </c>
-      <c r="J47" t="s">
-        <v>283</v>
-      </c>
-      <c r="K47" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F48" t="s">
-        <v>195</v>
-      </c>
-      <c r="I48" t="s">
-        <v>293</v>
-      </c>
-      <c r="P48" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>6</v>
-      </c>
-      <c r="C49" t="s">
-        <v>292</v>
-      </c>
-      <c r="D49" t="s">
-        <v>295</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F49" t="s">
-        <v>195</v>
-      </c>
-      <c r="I49" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>6</v>
-      </c>
-      <c r="C50" t="s">
-        <v>292</v>
-      </c>
-      <c r="D50" t="s">
-        <v>296</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F50" t="s">
-        <v>195</v>
-      </c>
-      <c r="I50" t="s">
-        <v>298</v>
-      </c>
-      <c r="P50" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5" t="s">
+    </row>
+    <row r="61" spans="1:15">
+      <c r="B61" t="s">
         <v>349</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="F51" t="s">
-        <v>195</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>6</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F52" t="s">
-        <v>195</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A53" s="7">
-        <v>7</v>
-      </c>
-      <c r="B53" t="s">
-        <v>300</v>
-      </c>
-      <c r="D53" t="s">
-        <v>301</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="F61" s="6"/>
+      <c r="G61" t="s">
         <v>350</v>
       </c>
-      <c r="F53" t="s">
-        <v>195</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>7</v>
-      </c>
-      <c r="D54" t="s">
-        <v>302</v>
-      </c>
-      <c r="E54" s="7" t="s">
+    </row>
+    <row r="62" spans="1:15">
+      <c r="B62" t="s">
+        <v>351</v>
+      </c>
+      <c r="F62" s="8"/>
+      <c r="G62" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="F63" s="7"/>
+      <c r="G63" t="s">
         <v>353</v>
       </c>
-      <c r="F54" t="s">
-        <v>195</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P54" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>7</v>
-      </c>
-      <c r="D55" t="s">
-        <v>304</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F55" t="s">
-        <v>195</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P55" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A56" s="7">
-        <v>8</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D56" t="s">
-        <v>306</v>
-      </c>
-      <c r="E56" t="s">
-        <v>306</v>
-      </c>
-      <c r="F56" t="s">
-        <v>195</v>
-      </c>
-      <c r="I56" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A57" s="7">
-        <v>9</v>
-      </c>
-      <c r="B57" t="s">
-        <v>308</v>
-      </c>
-      <c r="D57" t="s">
-        <v>364</v>
-      </c>
-      <c r="E57" t="s">
-        <v>361</v>
-      </c>
-      <c r="F57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>9</v>
-      </c>
-      <c r="D58" t="s">
-        <v>365</v>
-      </c>
-      <c r="E58" t="s">
-        <v>362</v>
-      </c>
-      <c r="F58" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>9</v>
-      </c>
-      <c r="D59" t="s">
-        <v>310</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F59" t="s">
-        <v>195</v>
-      </c>
-      <c r="I59" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>9</v>
-      </c>
-      <c r="D60" t="s">
-        <v>313</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F60" t="s">
-        <v>315</v>
-      </c>
-      <c r="O60" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A61" s="7">
-        <v>3</v>
-      </c>
-      <c r="B61" t="s">
-        <v>317</v>
-      </c>
-      <c r="D61" t="s">
-        <v>318</v>
-      </c>
-      <c r="E61" t="s">
-        <v>319</v>
-      </c>
-      <c r="F61" t="s">
-        <v>195</v>
-      </c>
-      <c r="G61" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>3</v>
-      </c>
-      <c r="D62" t="s">
-        <v>320</v>
-      </c>
-      <c r="E62" t="s">
-        <v>321</v>
-      </c>
-      <c r="F62" t="s">
-        <v>195</v>
-      </c>
-      <c r="G62" t="s">
-        <v>322</v>
-      </c>
-      <c r="I62" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>3</v>
-      </c>
-      <c r="D63" t="s">
-        <v>323</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="F63" t="s">
-        <v>195</v>
-      </c>
-      <c r="G63" t="s">
-        <v>322</v>
-      </c>
-      <c r="I63" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A64" s="7">
-        <v>10</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D64" t="s">
-        <v>326</v>
-      </c>
-      <c r="F64" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>10</v>
-      </c>
-      <c r="D65" t="s">
-        <v>328</v>
-      </c>
-      <c r="F65" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>10</v>
-      </c>
-      <c r="D66" t="s">
-        <v>329</v>
-      </c>
-      <c r="F66" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>10</v>
-      </c>
-      <c r="D67" t="s">
-        <v>330</v>
-      </c>
-      <c r="F67" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>10</v>
-      </c>
-      <c r="D68" t="s">
-        <v>331</v>
-      </c>
-      <c r="F68" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>5</v>
-      </c>
-      <c r="C69" t="s">
-        <v>351</v>
-      </c>
-      <c r="D69" t="s">
-        <v>366</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="F69" t="s">
-        <v>195</v>
-      </c>
-      <c r="I69" t="s">
-        <v>203</v>
-      </c>
-      <c r="P69" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>5</v>
-      </c>
-      <c r="C70" t="s">
-        <v>351</v>
-      </c>
-      <c r="D70" t="s">
-        <v>367</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="F70" t="s">
-        <v>195</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="P70" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>5</v>
-      </c>
-      <c r="C71" t="s">
-        <v>347</v>
-      </c>
-      <c r="D71" t="s">
-        <v>335</v>
-      </c>
-      <c r="E71" t="s">
-        <v>336</v>
-      </c>
-      <c r="F71" t="s">
-        <v>195</v>
-      </c>
-      <c r="I71" t="s">
-        <v>74</v>
-      </c>
-    </row>
+    </row>
+    <row r="64" spans="1:15" ht="15"/>
+    <row r="68" ht="15"/>
+    <row r="70" ht="15"/>
+    <row r="74" ht="15"/>
+    <row r="75" ht="15"/>
+    <row r="81" ht="15"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R55">
+    <sortCondition ref="A2:A55"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5643,31 +5574,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9B6005-6F43-4EB4-8661-C70A2093261E}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="C1" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="D1" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="E1" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="F1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -5679,9 +5610,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -5693,9 +5624,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -5707,9 +5638,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -5721,9 +5652,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -5735,9 +5666,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -5749,9 +5680,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -5763,9 +5694,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -5777,9 +5708,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -5791,9 +5722,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -5805,9 +5736,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -5819,9 +5750,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -5833,9 +5764,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -5847,9 +5778,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -5861,9 +5792,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -5875,12 +5806,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B17" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C17">
         <v>60</v>
@@ -5889,12 +5820,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B18" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C18">
         <v>120</v>
@@ -5903,12 +5834,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B19" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C19">
         <v>30</v>
@@ -5917,12 +5848,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B20" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C20">
         <v>90</v>
@@ -5934,4 +5865,207 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E9B12C2B262A7D41BAA1C1A05186961E" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5712268625b41a295c1c13b9cc08810">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a4568ba-f362-4e84-99d7-dc60d25416b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2284d5a418b13d67f420d8f33de3453b" ns2:_="">
+    <xsd:import namespace="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a4568ba-f362-4e84-99d7-dc60d25416b3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4148a701-fb1a-48b4-b8a8-71c004994da9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D5C309B-A406-4F09-B9ED-A6A4D616E23D}"/>
 </file>